--- a/每日输出/高短/郑州-高短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/高短/郑州-高短-销售风灵在线率明细数据.xlsx
@@ -906,32 +906,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1688854668882689</t>
+          <t>1688855321663581</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>溯川向上-刘炎鹤</t>
+          <t>鼎立苍穹-吕萍</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>许圣虎</t>
+          <t>张海梅</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>xushenghu</t>
+          <t>zhanghaimei</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -943,7 +943,12 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -975,7 +980,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -985,7 +990,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1688856561832941</t>
+          <t>1688855521597371</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1000,17 +1005,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>朱草原</t>
+          <t>彭铖名</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>zhucaoyuan</t>
+          <t>pengchengming</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1029,7 +1034,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1064,32 +1069,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1688856890900501</t>
+          <t>1688855817803534</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>风禾尽起-陈春雨</t>
+          <t>鹏耀巅峰-孔坤朋</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>陈春雨</t>
+          <t>马国安</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>chenchunyu</t>
+          <t>maguoan</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1101,12 +1106,7 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -1148,32 +1148,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1688856152906822</t>
+          <t>1688855008853430</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>鹏耀巅峰-孔坤朋</t>
+          <t>追求卓越-白志勇</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>陈丹丹</t>
+          <t>马雨菡</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>chendandan</t>
+          <t>mayuhan</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1227,32 +1227,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1688856053774681</t>
+          <t>1688855819651492</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>鼎立苍穹-吕萍</t>
+          <t>风禾尽起-陈春雨</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>陈小龙</t>
+          <t>秦盈盈</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>chenxiaolong01</t>
+          <t>qinyingying</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1306,32 +1306,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1688854336892123</t>
+          <t>1688855135852328</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>风禾尽起-陈春雨</t>
+          <t>星火先锋-秦智豪</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>刘培豪</t>
+          <t>苏玉洁</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>liupeihao</t>
+          <t>suyujie</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1343,12 +1343,7 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1380,7 +1375,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1390,32 +1385,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1688857569853329</t>
+          <t>1688855111787697</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>勇立潮头-王雅欣</t>
+          <t>风禾尽起-陈春雨</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>李兵硕</t>
+          <t>曹文浩</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>libingshuo01</t>
+          <t>caowenhao</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1427,14 +1422,19 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1469,32 +1469,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1688855688851243</t>
+          <t>1688856349684264</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>鼎立苍穹-吕萍</t>
+          <t>溯川向上-刘炎鹤</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>韩国斌</t>
+          <t>刘炎鹤</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>hanguobin</t>
+          <t>liuyanhe</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>长期班</t>
+          <t>短期班</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1548,27 +1548,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1688857790811934</t>
+          <t>1688857283772451</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>六年级</t>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>王娅宁</t>
+          <t>张晨</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>wangyaning</t>
+          <t>zhangchen01</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1592,7 +1597,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1617,7 +1622,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1627,7 +1632,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1688855086939908</t>
+          <t>1688857489812364</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1637,22 +1642,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>同心致远-宋长金</t>
+          <t>凌云壮志-张海升</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>饶殷仕锦</t>
+          <t>李学刚</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>raoyinshijin</t>
+          <t>lixuegang</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1664,24 +1669,14 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>17,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1706,7 +1701,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1716,32 +1711,32 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1688857489812380</t>
+          <t>1688856077781011</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>同心致远-宋长金</t>
+          <t>风禾尽起-陈春雨</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>廖坤</t>
+          <t>魏君杰</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>liaokun</t>
+          <t>weijunjie</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1756,16 +1751,11 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1800,32 +1790,32 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1688856393577928</t>
+          <t>1688857818803046</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>风禾尽起-陈春雨</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>邢若湘</t>
+          <t>范玉琴</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>xingruoxiang</t>
+          <t>fanyuqin</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1837,7 +1827,12 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1879,32 +1874,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1688854681879377</t>
+          <t>1688856890900501</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>薪耀巅峰-李新</t>
+          <t>风禾尽起-陈春雨</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>李世华</t>
+          <t>陈春雨</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>lishihua</t>
+          <t>chenchunyu</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1913,13 +1908,28 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1958,7 +1968,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1688858441529988</t>
+          <t>1688854765669082</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1973,17 +1983,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>杨化龙</t>
+          <t>杨龙祥</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>yanghualong</t>
+          <t>yanglongxiang</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2027,7 +2037,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2037,32 +2047,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1688855521597371</t>
+          <t>1688856077781007</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>风禾尽起-陈春雨</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>彭铖名</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>pengchengming</t>
+          <t>lixinyi</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2081,7 +2091,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2116,32 +2126,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1688857067916233</t>
+          <t>1688857718881874</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>追求卓越-白志勇</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>崔成杰</t>
+          <t>孙欣雨</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>cuichengjie</t>
+          <t>sunxinyu01</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2153,7 +2163,12 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
@@ -2180,7 +2195,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>短期班</t>
+          <t>长期班</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2195,32 +2210,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1688856122908594</t>
+          <t>1688857790811934</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>高一</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>南征北战-张胜迪</t>
+          <t>六年级</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>张胜迪</t>
+          <t>王娅宁</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>zhangshengdi</t>
+          <t>wangyaning</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2269,7 +2279,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2279,7 +2289,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1688854525914367</t>
+          <t>1688855822752630</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2289,46 +2299,41 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>南征北战-张胜迪</t>
+          <t>风禾尽起-陈春雨</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>张芊芊</t>
+          <t>李东博</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>zhangqianqian03</t>
+          <t>lidongbo</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2353,7 +2358,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2363,32 +2368,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1688858111684229</t>
+          <t>1688855086939908</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>鼎立苍穹-吕萍</t>
+          <t>同心致远-宋长金</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>王豪爽</t>
+          <t>饶殷仕锦</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>wanghaoshuang</t>
+          <t>raoyinshijin</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2407,7 +2412,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2442,32 +2447,32 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1688854953914692</t>
+          <t>1688854940881881</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>追求卓越-白志勇</t>
+          <t>鹏耀巅峰-孔坤朋</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>任新雨</t>
+          <t>王艳涛</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>renxinyu</t>
+          <t>wangyantao</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2479,12 +2484,7 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1688858113742724</t>
+          <t>1688858283619541</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2536,22 +2536,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>鹏耀巅峰-孔坤朋</t>
+          <t>同心致远-宋长金</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>乔亚威</t>
+          <t>贾强</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>qiaoyawei</t>
+          <t>jiaqiang</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -2605,32 +2605,32 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1688856152906708</t>
+          <t>1688855262871763</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>南征北战-张胜迪</t>
+          <t>薪耀巅峰-李新</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>李梦萍</t>
+          <t>郑晓雅</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>limengping</t>
+          <t>zhengxiaoya</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2642,10 +2642,20 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
+        </is>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2674,7 +2684,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2684,32 +2694,32 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1688855161889716</t>
+          <t>1688855688851215</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>鹏耀巅峰-孔坤朋</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>李云龙</t>
+          <t>李时海</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>liyunlong</t>
+          <t>lishihai</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2721,14 +2731,19 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -2753,7 +2768,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2763,32 +2778,32 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1688857489812364</t>
+          <t>1688857084733494</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>凌云壮志-张海升</t>
+          <t>追求卓越-白志勇</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>李学刚</t>
+          <t>余海</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>lixuegang</t>
+          <t>yuhai</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2807,7 +2822,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -2832,7 +2847,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2842,32 +2857,32 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1688856152906411</t>
+          <t>1688855001814620</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>薪耀巅峰-李新</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>王佳美</t>
+          <t>刘晓杰</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>wangjiamei</t>
+          <t>liuxiaojie</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2876,17 +2891,32 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>15,16,17</t>
+        </is>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17</t>
+        </is>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>15,16,17</t>
+        </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -2921,7 +2951,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1688856704752440</t>
+          <t>1688857489812380</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2936,17 +2966,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>孙欢欢</t>
+          <t>廖坤</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>sunhuanhuan</t>
+          <t>liaokun</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2961,7 +2991,12 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
+        </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2990,7 +3025,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3000,37 +3035,37 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1688857814474385</t>
+          <t>1688856253775723</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>星火先锋-秦智豪</t>
+          <t>风禾尽起-陈春雨</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>秦智豪</t>
+          <t>周雅婷</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>qinzhihao</t>
+          <t>zhouyating</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M28" t="n">
@@ -3040,16 +3075,11 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -3084,52 +3114,52 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1688855086939889</t>
+          <t>1688854525914367</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>同心致远-宋长金</t>
+          <t>南征北战-张胜迪</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>李权华</t>
+          <t>张芊芊</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>liquanhua</t>
+          <t>zhangqianqian03</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q29" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>12,13,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3168,7 +3198,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1688856182933228</t>
+          <t>1688854953914692</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3183,17 +3213,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>王智博</t>
+          <t>任新雨</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>wangzhibo</t>
+          <t>renxinyu</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3252,32 +3282,32 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1688854332655057</t>
+          <t>1688857814474385</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>星火先锋-秦智豪</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>李迪豪</t>
+          <t>秦智豪</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>lidihao</t>
+          <t>qinzhihao</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3331,32 +3361,32 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1688856520845746</t>
+          <t>1688857317577380</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>鼎立苍穹-吕萍</t>
+          <t>溯川向上-刘炎鹤</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>王源豪</t>
+          <t>范春艳</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>wangyuanhao</t>
+          <t>fanchunyan</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3400,7 +3430,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3410,32 +3440,32 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1688854765669082</t>
+          <t>1688854795908011</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>南征北战-张胜迪</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>杨龙祥</t>
+          <t>张琳鑫</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>yanglongxiang</t>
+          <t>zhanglinxin</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3447,11 +3477,11 @@
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>11,12,13</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q33" t="n">
@@ -3459,7 +3489,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -3494,7 +3524,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1688857384849805</t>
+          <t>1688858252870185</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3504,22 +3534,22 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>追求卓越-白志勇</t>
+          <t>南征北战-张胜迪</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>王森</t>
+          <t>凡栋程</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>wangsen</t>
+          <t>fandongcheng</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3531,12 +3561,7 @@
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
@@ -3568,7 +3593,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3578,32 +3603,32 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1688856835718975</t>
+          <t>1688856152906411</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>薪耀巅峰-李新</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>李志远</t>
+          <t>王佳美</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>lizhiyuan01</t>
+          <t>wangjiamei</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3615,14 +3640,19 @@
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -3647,7 +3677,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3657,32 +3687,32 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1688854940881881</t>
+          <t>1688855974854090</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>鹏耀巅峰-孔坤朋</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>王艳涛</t>
+          <t>张园梦</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>wangyantao</t>
+          <t>zhangyuanmeng01</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3694,14 +3724,19 @@
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -3726,7 +3761,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3736,32 +3771,32 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1688855008853457</t>
+          <t>1688857814474642</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>追求卓越-白志勇</t>
+          <t>同心致远-宋长金</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>白志勇</t>
+          <t>张宇</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>baizhiyong</t>
+          <t>zhangyu</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3780,7 +3815,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -3805,7 +3840,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3815,32 +3850,32 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1688857157941973</t>
+          <t>1688858003480325</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>星火先锋-秦智豪</t>
+          <t>勇立潮头-王雅欣</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>刘畅</t>
+          <t>王雅欣</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>liuchang05</t>
+          <t>wangyaxin</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3852,19 +3887,14 @@
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -3899,32 +3929,32 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1688854900741943</t>
+          <t>1688854481498708</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>凌云壮志-张海升</t>
+          <t>勇立潮头-王雅欣</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>穆豆豆</t>
+          <t>张丽</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>mudoudou</t>
+          <t>zhangli</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3968,7 +3998,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3978,32 +4008,32 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1688855321663826</t>
+          <t>1688858371885202</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>星火先锋-秦智豪</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>刘振</t>
+          <t>周宇晨</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>liuzhen01</t>
+          <t>zhouyuchen</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4018,16 +4048,11 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -4062,32 +4087,32 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1688857384849786</t>
+          <t>1688856152906822</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>薪耀巅峰-李新</t>
+          <t>鹏耀巅峰-孔坤朋</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>贾晓阳</t>
+          <t>陈丹丹</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>jiaxiaoyang</t>
+          <t>chendandan</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4099,12 +4124,7 @@
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
@@ -4136,7 +4156,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4146,7 +4166,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1688858371885209</t>
+          <t>1688857865785470</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4161,17 +4181,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>孟园琪</t>
+          <t>李瑞瑞</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>mengyuanqi</t>
+          <t>liruirui01</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4183,19 +4203,24 @@
         <v>1</v>
       </c>
       <c r="O42" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -4230,32 +4255,32 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1688857752522030</t>
+          <t>1688857814474461</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>同心致远-宋长金</t>
+          <t>风禾尽起-陈春雨</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>宋长金</t>
+          <t>田亚茹</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>songchangjin</t>
+          <t>tianyaru</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4264,28 +4289,13 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4314,7 +4324,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4324,32 +4334,32 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1688858394784789</t>
+          <t>1688857384849786</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>溯川向上-刘炎鹤</t>
+          <t>薪耀巅峰-李新</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>高冲</t>
+          <t>贾晓阳</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>gaochong</t>
+          <t>jiaxiaoyang</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4361,14 +4371,19 @@
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -4403,7 +4418,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1688856152906708</t>
+          <t>1688858252870185</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4418,17 +4433,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>李梦萍</t>
+          <t>凡栋程</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>limengping</t>
+          <t>fandongcheng</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4482,7 +4497,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1688855321663581</t>
+          <t>1688854332655057</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4492,22 +4507,22 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>鼎立苍穹-吕萍</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>张海梅</t>
+          <t>李迪豪</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>zhanghaimei</t>
+          <t>lidihao</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4519,12 +4534,7 @@
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
@@ -4566,32 +4576,32 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1688855001814645</t>
+          <t>1688858394784789</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>鼎立苍穹-吕萍</t>
+          <t>溯川向上-刘炎鹤</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>郝雪龙</t>
+          <t>高冲</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>haoxuelong02</t>
+          <t>gaochong</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4603,12 +4613,7 @@
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
@@ -4640,7 +4645,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4650,32 +4655,32 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1688858149743451</t>
+          <t>1688855825830845</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>凌云壮志-张海升</t>
+          <t>南征北战-张胜迪</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>杨永昆</t>
+          <t>杨帆</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>yangyongkun</t>
+          <t>yangfan03</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4687,14 +4692,19 @@
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -4729,32 +4739,32 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1688855242858317</t>
+          <t>1688855321663826</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>凌云壮志-张海升</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>贾梦辉</t>
+          <t>刘振</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>jiamenghui</t>
+          <t>liuzhen01</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4766,12 +4776,7 @@
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
@@ -4813,7 +4818,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1688855974854090</t>
+          <t>1688856520845726</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4823,22 +4828,22 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>勇立潮头-王雅欣</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>张园梦</t>
+          <t>宋扬</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>zhangyuanmeng01</t>
+          <t>songyang01</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4850,11 +4855,11 @@
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15</t>
         </is>
       </c>
       <c r="Q50" t="n">
@@ -4887,7 +4892,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4897,7 +4902,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1688856908839615</t>
+          <t>1688858111684229</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4912,17 +4917,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>何泽惠</t>
+          <t>王豪爽</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>hezehui01</t>
+          <t>wanghaoshuang</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4941,7 +4946,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -4966,7 +4971,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4976,32 +4981,32 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1688856520845726</t>
+          <t>1688857384849805</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>勇立潮头-王雅欣</t>
+          <t>追求卓越-白志勇</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>宋扬</t>
+          <t>王森</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>songyang01</t>
+          <t>wangsen</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5010,32 +5015,22 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -5060,7 +5055,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5070,7 +5065,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1688858003480325</t>
+          <t>1688856182932415</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5080,22 +5075,22 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>勇立潮头-王雅欣</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>王雅欣</t>
+          <t>李嘉威</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>wangyaxin</t>
+          <t>lijiawei02</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5104,32 +5099,17 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -5154,7 +5134,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5164,32 +5144,32 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1688857718881874</t>
+          <t>1688856152906708</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>南征北战-张胜迪</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>孙欣雨</t>
+          <t>李梦萍</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>sunxinyu01</t>
+          <t>limengping</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5201,19 +5181,14 @@
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q54" t="n">
         <v>1</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -5263,7 +5238,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5327,7 +5302,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1688855744700500</t>
+          <t>1688857752522030</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5337,22 +5312,22 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>凌云壮志-张海升</t>
+          <t>同心致远-宋长金</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>刘梦华</t>
+          <t>宋长金</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>liumenghua</t>
+          <t>songchangjin</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5396,7 +5371,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5406,7 +5381,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1688856037697435</t>
+          <t>1688854640632036</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5416,22 +5391,22 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>勇立潮头-王雅欣</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>张梦豪</t>
+          <t>董哲</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>zhangmenghao</t>
+          <t>dongzhe</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5443,19 +5418,14 @@
         <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -5490,7 +5460,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1688857024825581</t>
+          <t>1688855157589831</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5500,22 +5470,22 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>鹏耀巅峰-孔坤朋</t>
+          <t>凌云壮志-张海升</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>郭东涵</t>
+          <t>王艳超</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>guodonghan</t>
+          <t>wangyanchao</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5569,7 +5539,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1688858252870185</t>
+          <t>1688856182933228</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5579,34 +5549,39 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>南征北战-张胜迪</t>
+          <t>追求卓越-白志勇</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>凡栋程</t>
+          <t>王智博</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fandongcheng</t>
+          <t>wangzhibo</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M59" t="n">
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q59" t="n">
         <v>1</v>
@@ -5648,7 +5623,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1688858429561203</t>
+          <t>1688855822752564</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5663,17 +5638,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>宋义庆</t>
+          <t>李显福</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>songyiqing</t>
+          <t>lixianfu</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5685,12 +5660,7 @@
         <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>6,7,8</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
@@ -5722,7 +5692,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5732,7 +5702,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1688855822752564</t>
+          <t>1688854481776996</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5742,22 +5712,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>勇立潮头-王雅欣</t>
+          <t>鼎立苍穹-吕萍</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>李显福</t>
+          <t>张银</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>lixianfu</t>
+          <t>zhangyin01</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5776,7 +5746,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -5811,32 +5781,32 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1688857283772451</t>
+          <t>1688855744700500</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>凌云壮志-张海升</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>张晨</t>
+          <t>刘梦华</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>zhangchen01</t>
+          <t>liumenghua</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5848,12 +5818,7 @@
         <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
@@ -5895,7 +5860,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1688857084733494</t>
+          <t>1688856152906708</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5905,27 +5870,27 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>追求卓越-白志勇</t>
+          <t>南征北战-张胜迪</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>余海</t>
+          <t>李梦萍</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>yuhai</t>
+          <t>limengping</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M63" t="n">
@@ -5964,7 +5929,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5974,32 +5939,32 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1688856330809510</t>
+          <t>1688856122908594</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>凌云壮志-张海升</t>
+          <t>南征北战-张胜迪</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>刘汉文</t>
+          <t>张胜迪</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>liuhanwen</t>
+          <t>zhangshengdi</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6011,14 +5976,19 @@
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q64" t="n">
         <v>1</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -6053,32 +6023,32 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1688854346786806</t>
+          <t>1688854668882689</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>溯川向上-刘炎鹤</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>张银龙</t>
+          <t>许圣虎</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>zhangyinlong01</t>
+          <t>xushenghu</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6090,12 +6060,7 @@
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q65" t="n">
         <v>1</v>
@@ -6127,7 +6092,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6137,7 +6102,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1688854308832626</t>
+          <t>1688855111787667</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6152,17 +6117,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>陈信哲</t>
+          <t>皇甫双林</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>chenxinzhe</t>
+          <t>huangfushuanglin</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6171,7 +6136,12 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>16,17,19</t>
+        </is>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -6182,11 +6152,16 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>16,17,19</t>
+        </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -6221,32 +6196,32 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1688855001814620</t>
+          <t>1688856912792528</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>鹏耀巅峰-孔坤朋</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>刘晓杰</t>
+          <t>吕浩宇</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>liuxiaojie</t>
+          <t>lvhaoyu</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6258,12 +6233,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
@@ -6305,32 +6275,32 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1688855822752630</t>
+          <t>1688858429561203</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>风禾尽起-陈春雨</t>
+          <t>勇立潮头-王雅欣</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>李东博</t>
+          <t>宋义庆</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>lidongbo</t>
+          <t>songyiqing</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6342,7 +6312,12 @@
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>6,7,14,15</t>
+        </is>
       </c>
       <c r="Q68" t="n">
         <v>1</v>
@@ -6384,7 +6359,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1688856978579347</t>
+          <t>1688856035841621</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6399,17 +6374,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>李珂珂</t>
+          <t>刘传波</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>likeke</t>
+          <t>liuchuanbo</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6453,7 +6428,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6463,32 +6438,32 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1688857992853306</t>
+          <t>1688856561832941</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>溯川向上-刘炎鹤</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>尚俊逸</t>
+          <t>朱草原</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>shangjunyi</t>
+          <t>zhucaoyuan</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6507,7 +6482,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -6542,32 +6517,32 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1688855262871257</t>
+          <t>1688856470815243</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>薪耀巅峰-李新</t>
+          <t>风禾尽起-陈春雨</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>王怡纯</t>
+          <t>李琳</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>wangyichun01</t>
+          <t>lilin01</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6576,28 +6551,13 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -6636,32 +6596,32 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1688854795908011</t>
+          <t>1688855262871675</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>南征北战-张胜迪</t>
+          <t>星火先锋-秦智豪</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>张琳鑫</t>
+          <t>朱六威</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>zhanglinxin</t>
+          <t>zhuliuwei</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6673,12 +6633,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q72" t="n">
         <v>1</v>
@@ -6720,32 +6675,32 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1688856912792528</t>
+          <t>1688856835718975</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>鹏耀巅峰-孔坤朋</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>吕浩宇</t>
+          <t>李志远</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>lvhaoyu</t>
+          <t>lizhiyuan01</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6789,7 +6744,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6799,32 +6754,32 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1688857317577380</t>
+          <t>1688855262871257</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>溯川向上-刘炎鹤</t>
+          <t>薪耀巅峰-李新</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>范春艳</t>
+          <t>王怡纯</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>fanchunyan</t>
+          <t>wangyichun01</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6836,14 +6791,24 @@
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>1</v>
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,21,22,23</t>
+        </is>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -6878,7 +6843,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1688855819651492</t>
+          <t>1688857992853306</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6888,22 +6853,22 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>风禾尽起-陈春雨</t>
+          <t>溯川向上-刘炎鹤</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>秦盈盈</t>
+          <t>尚俊逸</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>qinyingying</t>
+          <t>shangjunyi</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6957,32 +6922,32 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1688855745745486</t>
+          <t>1688856035841655</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>凌云壮志-张海升</t>
+          <t>鼎立苍穹-吕萍</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>任世豪</t>
+          <t>杨妍</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>renshihao01</t>
+          <t>yangyan04</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7031,7 +6996,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7041,32 +7006,32 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1688857396721046</t>
+          <t>1688855086939889</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>溯川向上-刘炎鹤</t>
+          <t>同心致远-宋长金</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>于香</t>
+          <t>李权华</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>yuxiang</t>
+          <t>liquanhua</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7078,14 +7043,24 @@
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="Q77" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -7110,7 +7085,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7120,51 +7095,56 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1688856253775723</t>
+          <t>1688856981879376</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>风禾尽起-陈春雨</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>周雅婷</t>
+          <t>冯科皓</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>zhouyating</t>
+          <t>fengkehao</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M78" t="n">
         <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q78" t="n">
         <v>1</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -7199,32 +7179,32 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1688856053593867</t>
+          <t>1688856725829020</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>星火先锋-秦智豪</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>尤振中</t>
+          <t>王照玺</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>youzhenzhong</t>
+          <t>wangzhaoxi</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7236,12 +7216,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q79" t="n">
         <v>1</v>
@@ -7273,7 +7248,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7283,32 +7258,32 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1688854640632036</t>
+          <t>1688855170864409</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>勇立潮头-王雅欣</t>
+          <t>同心致远-宋长金</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>董哲</t>
+          <t>齐苗苗</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>dongzhe</t>
+          <t>qimiaomiao</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7320,14 +7295,19 @@
         <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q80" t="n">
         <v>1</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -7362,32 +7342,32 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1688857814474461</t>
+          <t>1688856015648369</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>风禾尽起-陈春雨</t>
+          <t>凌云壮志-张海升</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>田亚茹</t>
+          <t>张海升</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>tianyaru</t>
+          <t>zhanghaisheng</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7399,12 +7379,7 @@
         <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q81" t="n">
         <v>1</v>
@@ -7446,7 +7421,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1688856152906651</t>
+          <t>1688857186875483</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7456,22 +7431,22 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>追求卓越-白志勇</t>
+          <t>南征北战-张胜迪</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>陈瑞阳</t>
+          <t>吴慧娟</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>chenruiyang</t>
+          <t>wuhuijuan</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -7483,7 +7458,12 @@
         <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10</t>
+        </is>
       </c>
       <c r="Q82" t="n">
         <v>1</v>
@@ -7515,7 +7495,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7525,32 +7505,32 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1688855262871763</t>
+          <t>1688857551486684</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>薪耀巅峰-李新</t>
+          <t>勇立潮头-王雅欣</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>郑晓雅</t>
+          <t>孔苗苗</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>zhengxiaoya</t>
+          <t>kongmiaomiao</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7562,11 +7542,11 @@
         <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>9,10,11</t>
         </is>
       </c>
       <c r="Q83" t="n">
@@ -7574,7 +7554,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -7609,32 +7589,32 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1688857120836023</t>
+          <t>1688854681879377</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>鹏耀巅峰-孔坤朋</t>
+          <t>薪耀巅峰-李新</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>贾江洋</t>
+          <t>李世华</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>jiajiangyang</t>
+          <t>lishihua</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7646,12 +7626,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q84" t="n">
         <v>1</v>
@@ -7683,7 +7658,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7693,32 +7668,32 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1688855817803534</t>
+          <t>1688857067916233</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>鹏耀巅峰-孔坤朋</t>
+          <t>追求卓越-白志勇</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>马国安</t>
+          <t>崔成杰</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>maguoan</t>
+          <t>cuichengjie</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7737,7 +7712,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
@@ -7762,7 +7737,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7772,7 +7747,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1688855008853430</t>
+          <t>1688857396721046</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7782,22 +7757,22 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>追求卓越-白志勇</t>
+          <t>溯川向上-刘炎鹤</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>马雨菡</t>
+          <t>于香</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>mayuhan</t>
+          <t>yuxiang</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7816,7 +7791,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -7841,7 +7816,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7851,32 +7826,32 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1688855248814337</t>
+          <t>1688855097779421</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>同心致远-宋长金</t>
+          <t>溯川向上-刘炎鹤</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>李建刚</t>
+          <t>杨靖宇</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>lijiangang</t>
+          <t>yangjingyu</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7888,19 +7863,14 @@
         <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q87" t="n">
         <v>1</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -7925,7 +7895,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7935,32 +7905,32 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1688857865785470</t>
+          <t>1688856037697435</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>鹏耀巅峰-孔坤朋</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>李瑞瑞</t>
+          <t>张梦豪</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>liruirui01</t>
+          <t>zhangmenghao</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7984,7 +7954,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -8009,7 +7979,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8019,32 +7989,32 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1688856349684264</t>
+          <t>1688855248814337</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>溯川向上-刘炎鹤</t>
+          <t>同心致远-宋长金</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>刘炎鹤</t>
+          <t>李建刚</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>liuyanhe</t>
+          <t>lijiangang</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -8056,14 +8026,19 @@
         <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q89" t="n">
         <v>1</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -8098,32 +8073,32 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1688855157589831</t>
+          <t>1688856520845746</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>凌云壮志-张海升</t>
+          <t>鼎立苍穹-吕萍</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>王艳超</t>
+          <t>王源豪</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>wangyanchao</t>
+          <t>wangyuanhao</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8135,7 +8110,12 @@
         <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>11,12,13,14,15,16,17,18,19</t>
+        </is>
       </c>
       <c r="Q90" t="n">
         <v>1</v>
@@ -8167,7 +8147,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8177,7 +8157,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1688858252870185</t>
+          <t>1688856393577928</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -8187,22 +8167,22 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>南征北战-张胜迪</t>
+          <t>风禾尽起-陈春雨</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>凡栋程</t>
+          <t>邢若湘</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>fandongcheng</t>
+          <t>xingruoxiang</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -8221,7 +8201,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
@@ -8246,7 +8226,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8256,32 +8236,32 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1688856108862251</t>
+          <t>1688857992853339</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>南征北战-张胜迪</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>刘一润</t>
+          <t>钟毅</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>liuyirun</t>
+          <t>zhongyi</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -8293,19 +8273,14 @@
         <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q92" t="n">
         <v>1</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
@@ -8330,7 +8305,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8340,32 +8315,32 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1688856077781007</t>
+          <t>1688856053593867</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>风禾尽起-陈春雨</t>
+          <t>星火先锋-秦智豪</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>李欣怡</t>
+          <t>尤振中</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>lixinyi</t>
+          <t>youzhenzhong</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -8384,7 +8359,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
@@ -8409,7 +8384,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8419,32 +8394,32 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1688856015648369</t>
+          <t>1688854336892123</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>凌云壮志-张海升</t>
+          <t>风禾尽起-陈春雨</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>张海升</t>
+          <t>刘培豪</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>zhanghaisheng</t>
+          <t>liupeihao</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -8460,7 +8435,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q94" t="n">
@@ -8468,7 +8443,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
@@ -8503,7 +8478,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1688857551486684</t>
+          <t>1688855688851243</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -8513,22 +8488,22 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>勇立潮头-王雅欣</t>
+          <t>鼎立苍穹-吕萍</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>孔苗苗</t>
+          <t>韩国斌</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>kongmiaomiao</t>
+          <t>hanguobin</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -8582,32 +8557,32 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1688856035841621</t>
+          <t>1688857198671302</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>溯川向上-刘炎鹤</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>刘传波</t>
+          <t>韩家宝</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>liuchuanbo</t>
+          <t>hanjiabao</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -8619,7 +8594,12 @@
         <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>9,10,11,12</t>
+        </is>
       </c>
       <c r="Q96" t="n">
         <v>1</v>
@@ -8651,7 +8631,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8661,7 +8641,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1688856152906616</t>
+          <t>1688856704752440</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8671,22 +8651,22 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>鹏耀巅峰-孔坤朋</t>
+          <t>同心致远-宋长金</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>沈欣欣</t>
+          <t>孙欢欢</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>shenxinxin</t>
+          <t>sunhuanhuan</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8705,7 +8685,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
@@ -8730,7 +8710,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8740,7 +8720,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1688856011862218</t>
+          <t>1688855745745486</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8750,22 +8730,22 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>鹏耀巅峰-孔坤朋</t>
+          <t>凌云壮志-张海升</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>翟帅楠</t>
+          <t>任世豪</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>zhaishuainan</t>
+          <t>renshihao01</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -8774,32 +8754,22 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>0.7777777777777778</v>
+        <v>0</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>10,11,12,13</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -8834,7 +8804,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1688856981879376</t>
+          <t>1688856053774681</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -8844,22 +8814,22 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>鼎立苍穹-吕萍</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>冯科皓</t>
+          <t>陈小龙</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>fengkehao</t>
+          <t>chenxiaolong01</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -8871,12 +8841,7 @@
         <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q99" t="n">
         <v>1</v>
@@ -8908,7 +8873,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8918,32 +8883,32 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1688857992853339</t>
+          <t>1688856152906616</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>鹏耀巅峰-孔坤朋</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>钟毅</t>
+          <t>沈欣欣</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>zhongyi</t>
+          <t>shenxinxin</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -8962,7 +8927,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
@@ -8987,7 +8952,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8997,32 +8962,32 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1688856035841655</t>
+          <t>1688856011862218</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>鼎立苍穹-吕萍</t>
+          <t>鹏耀巅峰-孔坤朋</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>杨妍</t>
+          <t>翟帅楠</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>yangyan04</t>
+          <t>zhaishuainan</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -9034,19 +8999,19 @@
         <v>1</v>
       </c>
       <c r="O101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q101" t="n">
         <v>0</v>
       </c>
-      <c r="P101" t="inlineStr">
+      <c r="R101" t="inlineStr">
         <is>
           <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
-      <c r="Q101" t="n">
-        <v>1</v>
-      </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
@@ -9071,7 +9036,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9081,32 +9046,32 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1688855097779421</t>
+          <t>1688855161889716</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>溯川向上-刘炎鹤</t>
+          <t>鹏耀巅峰-孔坤朋</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>杨靖宇</t>
+          <t>李云龙</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>yangjingyu</t>
+          <t>liyunlong</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -9125,7 +9090,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -9150,7 +9115,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9160,7 +9125,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1688857814474642</t>
+          <t>1688857120836023</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -9170,22 +9135,22 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>同心致远-宋长金</t>
+          <t>鹏耀巅峰-孔坤朋</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>张宇</t>
+          <t>贾江洋</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>zhangyu</t>
+          <t>jiajiangyang</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -9197,14 +9162,24 @@
         <v>1</v>
       </c>
       <c r="O103" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q103" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -9229,7 +9204,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9239,32 +9214,32 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1688856037697435</t>
+          <t>1688854308832626</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>同心致远-宋长金</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>张梦豪</t>
+          <t>陈信哲</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>zhangmenghao</t>
+          <t>chenxinzhe</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -9276,11 +9251,11 @@
         <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15</t>
         </is>
       </c>
       <c r="Q104" t="n">
@@ -9288,7 +9263,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -9323,32 +9298,32 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1688857359851192</t>
+          <t>1688856108862251</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>鼎立苍穹-吕萍</t>
+          <t>南征北战-张胜迪</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>孟祥瑞</t>
+          <t>刘一润</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>mengxiangrui</t>
+          <t>liuyirun</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -9397,7 +9372,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9407,32 +9382,32 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1688857186875483</t>
+          <t>1688855001814645</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>南征北战-张胜迪</t>
+          <t>鼎立苍穹-吕萍</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>吴慧娟</t>
+          <t>郝雪龙</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>wuhuijuan</t>
+          <t>haoxuelong02</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -9444,14 +9419,19 @@
         <v>1</v>
       </c>
       <c r="O106" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q106" t="n">
         <v>1</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
@@ -9486,7 +9466,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1688857198671302</t>
+          <t>1688855797819236</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -9501,17 +9481,17 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>韩家宝</t>
+          <t>叶妞妞</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>hanjiabao</t>
+          <t>yeniuniu</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -9565,32 +9545,32 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1688856470815243</t>
+          <t>1688857359851192</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>风禾尽起-陈春雨</t>
+          <t>鼎立苍穹-吕萍</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>李琳</t>
+          <t>孟祥瑞</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>lilin01</t>
+          <t>mengxiangrui</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -9602,7 +9582,12 @@
         <v>1</v>
       </c>
       <c r="O108" t="n">
-        <v>1</v>
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q108" t="n">
         <v>1</v>
@@ -9644,32 +9629,32 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1688857004722605</t>
+          <t>1688854900741943</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>鼎立苍穹-吕萍</t>
+          <t>凌云壮志-张海升</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>高凯</t>
+          <t>穆豆豆</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>gaokai</t>
+          <t>mudoudou</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -9713,7 +9698,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9723,7 +9708,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1688855170864409</t>
+          <t>1688856330809510</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -9733,22 +9718,22 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>同心致远-宋长金</t>
+          <t>凌云壮志-张海升</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>齐苗苗</t>
+          <t>刘汉文</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>qimiaomiao</t>
+          <t>liuhanwen</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -9760,11 +9745,11 @@
         <v>1</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15</t>
         </is>
       </c>
       <c r="Q110" t="n">
@@ -9772,7 +9757,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
@@ -9807,7 +9792,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1688857818803046</t>
+          <t>1688857865785379</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9817,22 +9802,22 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>勇立潮头-王雅欣</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>范玉琴</t>
+          <t>葛增光</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>fanyuqin</t>
+          <t>gezengguang</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -9844,12 +9829,7 @@
         <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q111" t="n">
         <v>1</v>
@@ -9891,32 +9871,32 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1688856077781011</t>
+          <t>1688855262871647</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>风禾尽起-陈春雨</t>
+          <t>星火先锋-秦智豪</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>魏君杰</t>
+          <t>邱嘉豪</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>weijunjie</t>
+          <t>qiujiahao</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -9970,7 +9950,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1688855797819236</t>
+          <t>1688857569853329</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -9980,22 +9960,22 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>勇立潮头-王雅欣</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>叶妞妞</t>
+          <t>李兵硕</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>yeniuniu</t>
+          <t>libingshuo01</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -10049,32 +10029,32 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1688854481776996</t>
+          <t>1688855008853457</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>鼎立苍穹-吕萍</t>
+          <t>追求卓越-白志勇</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>张银</t>
+          <t>白志勇</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>zhangyin01</t>
+          <t>baizhiyong</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -10086,12 +10066,7 @@
         <v>1</v>
       </c>
       <c r="O114" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q114" t="n">
         <v>1</v>
@@ -10123,7 +10098,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10133,32 +10108,32 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1688854642873440</t>
+          <t>1688858149743465</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>薪耀巅峰-李新</t>
+          <t>勇立潮头-王雅欣</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>李新</t>
+          <t>乔淑涵</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>lixin05</t>
+          <t>qiaoshuhan</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -10170,19 +10145,14 @@
         <v>1</v>
       </c>
       <c r="O115" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>11,12,13,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q115" t="n">
         <v>1</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
@@ -10207,7 +10177,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10217,32 +10187,32 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1688856182932415</t>
+          <t>1688858149743451</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>凌云壮志-张海升</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>李嘉威</t>
+          <t>杨永昆</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>lijiawei02</t>
+          <t>yangyongkun</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -10261,7 +10231,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -10286,7 +10256,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10296,7 +10266,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1688857865785379</t>
+          <t>1688856037697435</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -10306,22 +10276,22 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>勇立潮头-王雅欣</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>葛增光</t>
+          <t>张梦豪</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>gezengguang</t>
+          <t>zhangmenghao</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -10333,14 +10303,19 @@
         <v>1</v>
       </c>
       <c r="O117" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q117" t="n">
         <v>1</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -10365,7 +10340,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10375,32 +10350,32 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1688858371885202</t>
+          <t>1688857024825581</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>星火先锋-秦智豪</t>
+          <t>鹏耀巅峰-孔坤朋</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>周宇晨</t>
+          <t>郭东涵</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>zhouyuchen</t>
+          <t>guodonghan</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -10412,19 +10387,24 @@
         <v>1</v>
       </c>
       <c r="O118" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q118" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14,15,16</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
@@ -10449,7 +10429,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10459,7 +10439,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1688858283619541</t>
+          <t>1688858113742724</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -10469,22 +10449,22 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>同心致远-宋长金</t>
+          <t>鹏耀巅峰-孔坤朋</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>贾强</t>
+          <t>乔亚威</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>jiaqiang</t>
+          <t>qiaoyawei</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -10503,7 +10483,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
@@ -10538,7 +10518,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1688855135852328</t>
+          <t>1688857157941973</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -10553,17 +10533,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>苏玉洁</t>
+          <t>刘畅</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>suyujie</t>
+          <t>liuchang05</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -10572,13 +10552,28 @@
         </is>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="O120" t="n">
-        <v>1</v>
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
       </c>
       <c r="Q120" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -10607,7 +10602,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10617,7 +10612,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1688858149743465</t>
+          <t>1688856908839615</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -10627,22 +10622,22 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>勇立潮头-王雅欣</t>
+          <t>鼎立苍穹-吕萍</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>乔淑涵</t>
+          <t>何泽惠</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>qiaoshuhan</t>
+          <t>hezehui01</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -10661,7 +10656,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
@@ -10696,32 +10691,32 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>1688855688851215</t>
+          <t>1688856978579347</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>溯川向上-刘炎鹤</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>李时海</t>
+          <t>李珂珂</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>lishihai</t>
+          <t>likeke</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -10733,12 +10728,7 @@
         <v>1</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q122" t="n">
         <v>1</v>
@@ -10780,37 +10770,37 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>1688856077780999</t>
+          <t>1688858371885209</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>南征北战-张胜迪</t>
+          <t>鹏耀巅峰-孔坤朋</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>张作</t>
+          <t>孟园琪</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>zhangzuo</t>
+          <t>mengyuanqi</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M123" t="n">
@@ -10849,7 +10839,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -10859,32 +10849,32 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>1688855111787697</t>
+          <t>1688854346786806</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>风禾尽起-陈春雨</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>曹文浩</t>
+          <t>张银龙</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>caowenhao</t>
+          <t>zhangyinlong01</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -10908,7 +10898,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
@@ -10943,7 +10933,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1688854481498708</t>
+          <t>1688858441529988</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -10953,22 +10943,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>勇立潮头-王雅欣</t>
+          <t>青云折桂-彭铖名</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>张丽</t>
+          <t>杨化龙</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>zhangli</t>
+          <t>yanghualong</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -11022,7 +11012,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1688855825830845</t>
+          <t>1688856077780999</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -11037,34 +11027,29 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>杨帆</t>
+          <t>张作</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>yangfan03</t>
+          <t>zhangzuo</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M126" t="n">
         <v>1</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q126" t="n">
         <v>1</v>
@@ -11096,7 +11081,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11106,32 +11091,32 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>1688855262871675</t>
+          <t>1688857004722605</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>星火先锋-秦智豪</t>
+          <t>鼎立苍穹-吕萍</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>朱六威</t>
+          <t>高凯</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>zhuliuwei</t>
+          <t>gaokai</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -11150,7 +11135,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -11185,32 +11170,32 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>1688855111787667</t>
+          <t>1688854642873440</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>同心致远-宋长金</t>
+          <t>薪耀巅峰-李新</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>皇甫双林</t>
+          <t>李新</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>huangfushuanglin</t>
+          <t>lixin05</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -11219,28 +11204,13 @@
         </is>
       </c>
       <c r="M128" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O128" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q128" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R128" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -11279,7 +11249,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1688856725829020</t>
+          <t>1688856159893031</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -11294,17 +11264,17 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>王照玺</t>
+          <t>罗豪威</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>wangzhaoxi</t>
+          <t>luohaowei</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -11313,28 +11283,18 @@
         </is>
       </c>
       <c r="M129" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O129" t="n">
-        <v>0.7777777777777778</v>
+        <v>0</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>9,10,11,12</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="R129" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -11373,32 +11333,32 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1688856159893031</t>
+          <t>1688855242858317</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>凌云壮志-张海升</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>罗豪威</t>
+          <t>贾梦辉</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>luohaowei</t>
+          <t>jiamenghui</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -11410,11 +11370,11 @@
         <v>1</v>
       </c>
       <c r="O130" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>9,10,11,12,16,17,18,19</t>
         </is>
       </c>
       <c r="Q130" t="n">
@@ -11457,32 +11417,32 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>1688855262871647</t>
+          <t>1688856152906651</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>星火先锋-秦智豪</t>
+          <t>追求卓越-白志勇</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>邱嘉豪</t>
+          <t>陈瑞阳</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>qiujiahao</t>
+          <t>chenruiyang</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -11586,16 +11546,16 @@
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="3">
@@ -11618,10 +11578,10 @@
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -11651,10 +11611,10 @@
         <v>0.7692307692307693</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.6153846153846154</v>
       </c>
     </row>
     <row r="5">
@@ -11683,10 +11643,10 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="6">
@@ -11773,16 +11733,16 @@
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="9">
@@ -11800,10 +11760,10 @@
         <v>37</v>
       </c>
       <c r="E9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" t="n">
-        <v>0.918918918918919</v>
+        <v>0.8918918918918919</v>
       </c>
       <c r="G9" t="n">
         <v>23</v>
@@ -11864,16 +11824,16 @@
         <v>11</v>
       </c>
       <c r="E11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="G11" t="n">
         <v>6</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
         <v>0.5454545454545454</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="12">
@@ -11896,16 +11856,16 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="13">
@@ -11923,16 +11883,16 @@
         <v>32</v>
       </c>
       <c r="E13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8125</v>
+        <v>0.78125</v>
       </c>
       <c r="G13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H13" t="n">
-        <v>0.59375</v>
+        <v>0.65625</v>
       </c>
     </row>
     <row r="14">
@@ -11955,10 +11915,10 @@
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>7</v>
@@ -11987,16 +11947,16 @@
         <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9545454545454546</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
@@ -12046,16 +12006,16 @@
         <v>44</v>
       </c>
       <c r="E17" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9318181818181818</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5681818181818182</v>
       </c>
     </row>
     <row r="18">
@@ -12073,16 +12033,16 @@
         <v>126</v>
       </c>
       <c r="E18" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8809523809523809</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G18" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5793650793650794</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
   </sheetData>
@@ -12112,7 +12072,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（高短）-7月23日</t>
+          <t>企微风灵全天在线情况通晒（高短）-7月24日</t>
         </is>
       </c>
       <c r="B1" s="9" t="n"/>
@@ -12203,16 +12163,16 @@
         <v>7</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G4" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4" s="21" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="5">
@@ -12227,10 +12187,10 @@
         <v>6</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>2</v>
@@ -12257,10 +12217,10 @@
         <v>0.7692307692307693</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" s="25" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.6153846153846154</v>
       </c>
     </row>
     <row r="7">
@@ -12285,10 +12245,10 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" s="21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="8">
@@ -12351,16 +12311,16 @@
         <v>11</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="11">
@@ -12375,10 +12335,10 @@
         <v>37</v>
       </c>
       <c r="E11" s="23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" s="25" t="n">
-        <v>0.918918918918919</v>
+        <v>0.8918918918918919</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>23</v>
@@ -12427,16 +12387,16 @@
         <v>11</v>
       </c>
       <c r="E13" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="G13" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="H13" s="21" t="n">
         <v>0.5454545454545454</v>
-      </c>
-      <c r="G13" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" s="21" t="n">
-        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="14">
@@ -12451,16 +12411,16 @@
         <v>12</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="15">
@@ -12475,16 +12435,16 @@
         <v>32</v>
       </c>
       <c r="E15" s="23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>0.8125</v>
+        <v>0.78125</v>
       </c>
       <c r="G15" s="23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H15" s="25" t="n">
-        <v>0.59375</v>
+        <v>0.65625</v>
       </c>
     </row>
     <row r="16">
@@ -12503,10 +12463,10 @@
         <v>10</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G16" s="17" t="n">
         <v>7</v>
@@ -12527,16 +12487,16 @@
         <v>22</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>0.9545454545454546</v>
+        <v>1</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
@@ -12575,16 +12535,16 @@
         <v>44</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>0.9318181818181818</v>
+        <v>1</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5681818181818182</v>
       </c>
     </row>
     <row r="20">
@@ -12603,16 +12563,16 @@
         <v>126</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>0.8809523809523809</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>0.5793650793650794</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
   </sheetData>
